--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.3.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 4.â€” An interesting</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN :: 16 × 20, 3 large drawers: the</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]rentes</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]rentes</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: symbol-only separator/garbage line :: 1914.</t>
@@ -642,7 +646,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L715: line starts with punctuation glued to text :: * SILK and CREPE KIMONAS. SEPARATE SKIRTS-In White</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Gleaner will be published on •</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -688,12 +692,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” AT-</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN :: mirror 16×18, 4 large drawers</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -705,7 +709,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -719,7 +723,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pear in the Saturday issue)</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -747,7 +755,7 @@
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | candidate OCR token mismatch vs other OCR: "VexedQ" vs "Vexed" :: Efforts io Settle VexedQ Question â€” Whole Trouble</t>
+          <t>L208: candidate OCR token mismatch vs other OCR: "VexedQ" vs "Vexed" :: Efforts io Settle VexedQ Question — Whole Trouble</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr"/>
@@ -763,12 +771,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ONLY, NLY, DRESSERSâ€”Surface</t>
+          <t>L120: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -780,17 +788,21 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L299: punctuation artifact: repeated periods :: TELEPHONE CO.. LTD</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ changes of advertisements ap- •</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -806,12 +818,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -834,12 +846,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ONLY, CHIFFONIERâ€”Ma-</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 4.â€”An interesting</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -851,17 +863,21 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L418: punctuation artifact: repeated periods :: That experiment....</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L715: line starts with punctuation glued to text :: * SILK and CREPE KIMONAS. SEPARATE SKIRTS-In White</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -905,12 +921,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUITE â€”</t>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+597D CJK UNIFIED IDEOGRAPH-597D | isolated marker/symbol line :: 好</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: letâ€� regiment.</t>
+          <t>L257: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Until further notice The •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -928,7 +944,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L580: punctuation artifact: repeated periods :: ......New Majestic</t>
+          <t>L299: punctuation artifact: repeated periods :: TELEPHONE CO.. LTD</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -972,19 +988,19 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: å¥½</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY, CHIFFONIER â€” Ma-</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Gleaner will be published on •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L129: isolated marker/symbol line :: 3</t>
+          <t>L120: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -995,7 +1011,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L582: punctuation artifact: repeated periods :: .. Keystone Comedy</t>
+          <t>L418: punctuation artifact: repeated periods :: That experiment....</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -1035,19 +1051,19 @@
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY, PARLOR SUITEâ€”</t>
+          <t>L260: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: res. • Saturdays at noon.•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: :</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1058,7 +1074,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L584: punctuation artifact: repeated periods :: ............3 Reels</t>
+          <t>L580: punctuation artifact: repeated periods :: ......New Majestic</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1098,19 +1114,19 @@
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | candidate OCR token mismatch vs other OCR: "VexedQ" vs "Vexed" :: Efforts io Settle VexedQ Question â€” Whole Trouble</t>
+          <t>L557: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY DINNER SETâ€”A very</t>
+          <t>L262: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Advertisers in order to have •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: 8</t>
+          <t>L129: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1121,7 +1137,7 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L586: punctuation artifact: repeated periods :: DEAD MAN'S SHOES ...........</t>
+          <t>L582: punctuation artifact: repeated periods :: .. Keystone Comedy</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1141,12 +1157,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1161,19 +1177,19 @@
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has paid attention â€”" has a lot to learn</t>
+          <t>L587: stray/suspicious non-ASCII glyph(s): U+FF08 FULLWIDTH LEFT PARENTHESIS :: THE （</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: what the neighbors say," she doesnâ€™t</t>
+          <t>L279: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CHATEAU €</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L132: isolated marker/symbol line :: 1</t>
+          <t>L130: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1184,7 +1200,7 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L588: punctuation artifact: repeated periods :: HIS SACRIFICE ..............</t>
+          <t>L584: punctuation artifact: repeated periods :: ............3 Reels</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1209,7 +1225,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1224,19 +1240,19 @@
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L301: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebec, Aug. 4.â€” Seven people,</t>
+          <t>L588: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Until further notice The â€¢</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ changes of advertisements ap- •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: i</t>
+          <t>L131: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1247,7 +1263,7 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L590: punctuation artifact: repeated periods :: SIDETRACKED BY SISTER ......</t>
+          <t>L586: punctuation artifact: repeated periods :: DEAD MAN'S SHOES ...........</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1267,12 +1283,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1285,21 +1301,17 @@
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Gleaner will be published on â€¢</t>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pear in the Saturday issue)</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: S</t>
+          <t>L132: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1310,7 +1322,7 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L592: punctuation artifact: repeated periods :: TOPLITSKY &amp; CO..............</t>
+          <t>L588: punctuation artifact: repeated periods :: HIS SACRIFICE ..............</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
@@ -1335,7 +1347,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1344,25 +1356,21 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): WAISTSIn (odd internal casing) :: LADIESâ€™WAISTSIn all the various kinds wanted by those who</t>
+          <t>L627: suspicious token(s): LADIES’WAISTSIn (odd internal casing) :: LADIES’WAISTSIn all the various kinds wanted by those who</t>
         </is>
       </c>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 32â€”Monahan, Mrs. T. V., res.</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: res. â€¢ Saturdays at noon.â€¢</t>
+          <t>L284: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ should have their copy at The •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L135: isolated marker/symbol line :: 4</t>
+          <t>L133: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1371,7 +1379,11 @@
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
-      <c r="Q13" s="1" t="inlineStr"/>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>L590: punctuation artifact: repeated periods :: SIDETRACKED BY SISTER ......</t>
+        </is>
+      </c>
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr"/>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1394,7 +1406,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1403,21 +1415,17 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L491: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: posal-discouraged itâ€”sneered at it.</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Advertisers in order to have â€¢</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Gleaner office not later than •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 2</t>
+          <t>L134: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1426,7 +1434,11 @@
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>L592: punctuation artifact: repeated periods :: TOPLITSKY &amp; CO..............</t>
+        </is>
+      </c>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr"/>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1458,21 +1470,17 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 32â€”Monahan, Mrs. T. V.,</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L135: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1513,21 +1521,17 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WEDNESDAY â€” THE</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 126-21â€”Kitchen, Mrs. S., res.</t>
+          <t>L287: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: &amp; noon •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 8</t>
+          <t>L136: stray/suspicious non-ASCII glyph(s): U+597D CJK UNIFIED IDEOGRAPH-597D | isolated marker/symbol line :: 好</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1568,21 +1572,17 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.30 â€” 10.30</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L279: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: CHATEAU â‚¬</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 0</t>
+          <t>L137: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1611,26 +1611,18 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A BRANDâ€”</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 2</t>
+          <t>L138: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: 1</t>
+          <t>L663: symbol-only separator/garbage line :: 7.30—10.30</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1654,26 +1646,18 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LADIESâ€™LONG COATS â€” Very Stylish, in Silk, Lace, Poplin,</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ changes of advertisements ap- â€¢</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 2</t>
+          <t>L139: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L734: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1697,26 +1681,18 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L620: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRETTY DRESSES â€” In Silk, White and Colored Serge, Linen</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L283: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ pear in the Saturday issue)</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L191: isolated marker/symbol line :: a</t>
+          <t>L140: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1740,26 +1716,18 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): WAISTSIn (odd internal casing) :: LADIESâ€™WAISTSIn all the various kinds wanted by those who</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ should have their copy at The â€¢</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L200: isolated marker/symbol line :: T</t>
+          <t>L142: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L761: isolated marker/symbol line :: (A</t>
+          <t>L757: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1784,19 +1752,19 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L285: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Gleaner office not later than â€¢</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="O22" s="1" t="inlineStr"/>
+          <t>L154: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>L761: isolated marker/symbol line :: (A</t>
+        </is>
+      </c>
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr"/>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1819,16 +1787,12 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 4.30 o'clock on Friday after-â€¢</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: s.,</t>
+          <t>L191: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1854,16 +1818,12 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: &amp; noon â€¢</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L365: isolated marker/symbol line :: 317</t>
+          <t>L200: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -1889,16 +1849,12 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L304: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Efforts to Settle Vexed Questionâ€” Whole Trouble</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L388: isolated marker/symbol line :: 0</t>
+          <t>L352: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1924,16 +1880,12 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebec, Aug. 4.â€”Seven people,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L406: isolated marker/symbol line :: 4</t>
+          <t>L363: isolated marker/symbol line :: s.,</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1959,16 +1911,12 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 5â€”The Daily Tele-</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L421: isolated marker/symbol line :: 9</t>
+          <t>L365: isolated marker/symbol line :: 317</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -1994,16 +1942,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L419: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has paid attentionâ€” has a lot to learn</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L426: isolated marker/symbol line :: &amp;</t>
+          <t>L388: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -2029,16 +1973,12 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: posalâ€”discouraged itâ€”sneered at it.</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L427: isolated marker/symbol line :: 4</t>
+          <t>L406: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -2064,16 +2004,12 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L463: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Sir Wilfrid Laurierâ€™s Government</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L413: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -2099,16 +2035,12 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Rev. Dr, W. H. Smithâ€™s Views</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: A</t>
+          <t>L421: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -2134,16 +2066,12 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L558: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: -_ /â€˜yers for those whom</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L426: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -2169,16 +2097,12 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LADIES' LONG COATSâ€” Very Stylish, in Silk, Lace, Poplin,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L592: isolated marker/symbol line :: -</t>
+          <t>L427: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2204,14 +2128,14 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.30â€”10.30</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>L557: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
       <c r="O34" s="1" t="inlineStr"/>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
@@ -2235,14 +2159,14 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRETTY DRESSES â€” In Silk, White and Colored Serge, Linen</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>L573: symbol-only separator/garbage line :: 7.30 — 10.30</t>
+        </is>
+      </c>
       <c r="O35" s="1" t="inlineStr"/>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
@@ -2266,14 +2190,14 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>L577: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O36" s="1" t="inlineStr"/>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
@@ -2297,14 +2221,14 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>L588: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
       <c r="O37" s="1" t="inlineStr"/>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
@@ -2317,6 +2241,37 @@
       <c r="X37" s="1" t="inlineStr"/>
       <c r="Y37" s="1" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr"/>
+      <c r="C38" s="1" t="inlineStr"/>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr"/>
+      <c r="G38" s="1" t="inlineStr"/>
+      <c r="H38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr"/>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
+      <c r="L38" s="1" t="inlineStr"/>
+      <c r="M38" s="1" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>L592: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr"/>
+      <c r="Q38" s="1" t="inlineStr"/>
+      <c r="R38" s="1" t="inlineStr"/>
+      <c r="S38" s="1" t="inlineStr"/>
+      <c r="T38" s="1" t="inlineStr"/>
+      <c r="U38" s="1" t="inlineStr"/>
+      <c r="V38" s="1" t="inlineStr"/>
+      <c r="W38" s="1" t="inlineStr"/>
+      <c r="X38" s="1" t="inlineStr"/>
+      <c r="Y38" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
